--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>21</t>
   </si>
   <si>
-    <t>R$ 5.787,37</t>
+    <t>R$ 5.803,27</t>
   </si>
   <si>
-    <t>61.3</t>
+    <t>61.4</t>
   </si>
   <si>
     <t>40.4</t>
   </si>
   <si>
-    <t>5.98</t>
+    <t>5.97</t>
   </si>
   <si>
     <t>21.0</t>
   </si>
   <si>
-    <t>8.3</t>
+    <t>8.4</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>33.6%</t>
+    <t>33.9%</t>
   </si>
   <si>
     <t>18.0%</t>
@@ -10175,7 +10175,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10205,18 +10205,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>8839.7800000000007</v>
+      </c>
+      <c r="N58" s="6">
+        <v>94</v>
+      </c>
       <c r="O58" s="6">
         <v>79</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.8292118279569891</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>19.676370886075947</v>
+      </c>
+      <c r="R58" s="8">
+        <v>9.1102564102564099</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.29113924050632911</v>
+      </c>
       <c r="U58" s="9">
         <v>0.13924050632911392</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-01).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>21</t>
+    <t>18</t>
   </si>
   <si>
-    <t>R$ 5.803,27</t>
+    <t>R$ 5.764,99</t>
   </si>
   <si>
-    <t>61.4</t>
+    <t>61.1</t>
   </si>
   <si>
     <t>40.4</t>
   </si>
   <si>
-    <t>5.97</t>
+    <t>6.01</t>
   </si>
   <si>
-    <t>21.0</t>
+    <t>21.1</t>
   </si>
   <si>
     <t>8.4</t>
@@ -959,7 +959,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>33.9%</t>
+    <t>34.1%</t>
   </si>
   <si>
     <t>18.0%</t>
@@ -6849,7 +6849,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6879,14 +6879,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>4216.9200000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>53</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>6.141346153846154</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>17.937983720930234</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.7670534883720936</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.37209302325581395</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9138,7 +9150,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9168,14 +9180,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>830.39999999999998</v>
+      </c>
+      <c r="N51" s="6">
+        <v>8</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.3562500000000002</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>27.274999999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>8.7916500000000006</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14840,7 +14864,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14868,14 +14892,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4898.6099999999997</v>
+      </c>
+      <c r="N89" s="6">
+        <v>49</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>13.197618367346939</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>37.671113333333331</v>
+      </c>
+      <c r="R89" s="8">
+        <v>12.401113333333333</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.066666666666666666</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
